--- a/tp.xlsx
+++ b/tp.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6800"/>
+    <workbookView windowWidth="19200" windowHeight="6800" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="61">
   <si>
     <t>Employee Id</t>
   </si>
@@ -47,136 +48,169 @@
     <t>Job Name</t>
   </si>
   <si>
-    <t>01-06-2024(Sat)</t>
-  </si>
-  <si>
-    <t>02-06-2024(Sun)</t>
-  </si>
-  <si>
-    <t>03-06-2024(Mon)</t>
-  </si>
-  <si>
-    <t>04-06-2024(Tue)</t>
-  </si>
-  <si>
-    <t>05-06-2024(Wed)</t>
-  </si>
-  <si>
-    <t>06-06-2024(Thu)</t>
-  </si>
-  <si>
-    <t>07-06-2024(Fri)</t>
-  </si>
-  <si>
-    <t>08-06-2024(Sat)</t>
-  </si>
-  <si>
-    <t>09-06-2024(Sun)</t>
-  </si>
-  <si>
-    <t>10-06-2024(Mon)</t>
-  </si>
-  <si>
-    <t>11-06-2024(Tue)</t>
-  </si>
-  <si>
-    <t>12-06-2024(Wed)</t>
-  </si>
-  <si>
-    <t>13-06-2024(Thu)</t>
-  </si>
-  <si>
-    <t>14-06-2024(Fri)</t>
-  </si>
-  <si>
-    <t>15-06-2024(Sat)</t>
-  </si>
-  <si>
-    <t>16-06-2024(Sun)</t>
-  </si>
-  <si>
-    <t>17-06-2024(Mon)</t>
-  </si>
-  <si>
-    <t>18-06-2024(Tue)</t>
-  </si>
-  <si>
-    <t>19-06-2024(Wed)</t>
-  </si>
-  <si>
-    <t>20-06-2024(Thu)</t>
-  </si>
-  <si>
-    <t>21-06-2024(Fri)</t>
-  </si>
-  <si>
-    <t>22-06-2024(Sat)</t>
-  </si>
-  <si>
-    <t>23-06-2024(Sun)</t>
-  </si>
-  <si>
-    <t>24-06-2024(Mon)</t>
-  </si>
-  <si>
-    <t>25-06-2024(Tue)</t>
-  </si>
-  <si>
-    <t>26-06-2024(Wed)</t>
-  </si>
-  <si>
-    <t>27-06-2024(Thu)</t>
-  </si>
-  <si>
-    <t>28-06-2024(Fri)</t>
-  </si>
-  <si>
-    <t>29-06-2024(Sat)</t>
-  </si>
-  <si>
-    <t>30-06-2024(Sun)</t>
+    <t>Is Manual</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>01-07-2024(Mon)</t>
+  </si>
+  <si>
+    <t>02-07-2024(Tue)</t>
+  </si>
+  <si>
+    <t>03-07-2024(Wed)</t>
+  </si>
+  <si>
+    <t>04-07-2024(Thu)</t>
+  </si>
+  <si>
+    <t>05-07-2024(Fri)</t>
+  </si>
+  <si>
+    <t>06-07-2024(Sat)</t>
+  </si>
+  <si>
+    <t>07-07-2024(Sun)</t>
+  </si>
+  <si>
+    <t>08-07-2024(Mon)</t>
+  </si>
+  <si>
+    <t>09-07-2024(Tue)</t>
+  </si>
+  <si>
+    <t>10-07-2024(Wed)</t>
+  </si>
+  <si>
+    <t>11-07-2024(Thu)</t>
+  </si>
+  <si>
+    <t>12-07-2024(Fri)</t>
+  </si>
+  <si>
+    <t>13-07-2024(Sat)</t>
+  </si>
+  <si>
+    <t>14-07-2024(Sun)</t>
+  </si>
+  <si>
+    <t>15-07-2024(Mon)</t>
+  </si>
+  <si>
+    <t>16-07-2024(Tue)</t>
+  </si>
+  <si>
+    <t>17-07-2024(Wed)</t>
+  </si>
+  <si>
+    <t>18-07-2024(Thu)</t>
+  </si>
+  <si>
+    <t>19-07-2024(Fri)</t>
+  </si>
+  <si>
+    <t>20-07-2024(Sat)</t>
+  </si>
+  <si>
+    <t>21-07-2024(Sun)</t>
+  </si>
+  <si>
+    <t>22-07-2024(Mon)</t>
+  </si>
+  <si>
+    <t>23-07-2024(Tue)</t>
+  </si>
+  <si>
+    <t>24-07-2024(Wed)</t>
+  </si>
+  <si>
+    <t>25-07-2024(Thu)</t>
+  </si>
+  <si>
+    <t>26-07-2024(Fri)</t>
+  </si>
+  <si>
+    <t>27-07-2024(Sat)</t>
+  </si>
+  <si>
+    <t>28-07-2024(Sun)</t>
+  </si>
+  <si>
+    <t>29-07-2024(Mon)</t>
+  </si>
+  <si>
+    <t>30-07-2024(Tue)</t>
+  </si>
+  <si>
+    <t>31-07-2024(Wed)</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
+    <t>INF-AHM-183</t>
+  </si>
+  <si>
     <t>Yash Upadhyaya</t>
   </si>
   <si>
-    <t>test@gmail.com</t>
+    <t>yash.upadhyaya@inferenz.ai</t>
+  </si>
+  <si>
+    <t>Inferenz</t>
+  </si>
+  <si>
+    <t>Research, Analysis and Training</t>
+  </si>
+  <si>
+    <t>AWS APN</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>04:00</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>Snowpro Core</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>Snowtrend</t>
+  </si>
+  <si>
+    <t>148:00</t>
+  </si>
+  <si>
+    <t>Snow</t>
+  </si>
+  <si>
+    <t>YES</t>
   </si>
   <si>
     <t>TEST</t>
   </si>
   <si>
-    <t>RND</t>
-  </si>
-  <si>
-    <t>JOB1</t>
-  </si>
-  <si>
-    <t>JOB2</t>
-  </si>
-  <si>
-    <t>JOB3</t>
-  </si>
-  <si>
-    <t>Meet</t>
-  </si>
-  <si>
-    <t>test`@gmail.com</t>
-  </si>
-  <si>
-    <t>AADSD</t>
-  </si>
-  <si>
-    <t>JOB4</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>0</t>
+    <t>180:00</t>
   </si>
 </sst>
 </file>
@@ -200,14 +234,6 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
@@ -218,6 +244,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -654,28 +688,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -799,14 +833,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1342,18 +1373,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="6"/>
+  <dimension ref="A1:AN6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="13.0909090909091" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="27.7272727272727" customWidth="1"/>
-    <col min="4" max="4" width="11.9090909090909" customWidth="1"/>
-    <col min="5" max="5" width="29.8181818181818" customWidth="1"/>
-    <col min="6" max="6" width="17.0909090909091" customWidth="1"/>
+    <col min="7" max="7" width="11.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:40">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1465,555 +1491,1221 @@
       <c r="AK1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
-      <c r="A2">
-        <v>113</v>
+    <row r="2" spans="1:40">
+      <c r="A2" t="s">
+        <v>40</v>
       </c>
       <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W2" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" t="s">
+        <v>48</v>
+      </c>
+      <c r="K3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L3" t="s">
+        <v>49</v>
+      </c>
+      <c r="M3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" t="s">
+        <v>47</v>
+      </c>
+      <c r="O3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" t="s">
+        <v>47</v>
+      </c>
+      <c r="T3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" t="s">
+        <v>47</v>
+      </c>
+      <c r="V3" t="s">
+        <v>47</v>
+      </c>
+      <c r="W3" t="s">
+        <v>47</v>
+      </c>
+      <c r="X3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" t="s">
+        <v>47</v>
+      </c>
+      <c r="L4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" t="s">
+        <v>47</v>
+      </c>
+      <c r="O4" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4" t="s">
+        <v>47</v>
+      </c>
+      <c r="V4" t="s">
+        <v>47</v>
+      </c>
+      <c r="W4" t="s">
+        <v>49</v>
+      </c>
+      <c r="X4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" t="s">
+        <v>47</v>
+      </c>
+      <c r="P5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" t="s">
+        <v>47</v>
+      </c>
+      <c r="U5" t="s">
+        <v>47</v>
+      </c>
+      <c r="V5" t="s">
+        <v>47</v>
+      </c>
+      <c r="W5" t="s">
+        <v>47</v>
+      </c>
+      <c r="X5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" t="s">
+        <v>49</v>
+      </c>
+      <c r="T6" t="s">
+        <v>49</v>
+      </c>
+      <c r="U6" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W6" t="s">
+        <v>49</v>
+      </c>
+      <c r="X6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:AN6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5"/>
+  <cols>
+    <col min="7" max="7" width="11.6363636363636" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:40">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="AM1" t="s">
         <v>38</v>
       </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40">
+      <c r="A2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
       <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3">
+        <v>4</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>8</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>8</v>
+      </c>
+      <c r="Q4">
+        <v>8</v>
+      </c>
+      <c r="R4">
+        <v>8</v>
+      </c>
+      <c r="S4">
+        <v>8</v>
+      </c>
+      <c r="T4">
+        <v>8</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>8</v>
+      </c>
+      <c r="X4">
+        <v>8</v>
+      </c>
+      <c r="Y4">
+        <v>8</v>
+      </c>
+      <c r="Z4">
+        <v>8</v>
+      </c>
+      <c r="AA4">
+        <v>4</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>8</v>
+      </c>
+      <c r="AE4">
+        <v>8</v>
+      </c>
+      <c r="AF4">
+        <v>8</v>
+      </c>
+      <c r="AG4">
+        <v>8</v>
+      </c>
+      <c r="AH4">
+        <v>8</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>8</v>
+      </c>
+      <c r="AL4">
+        <v>8</v>
+      </c>
+      <c r="AM4">
+        <v>8</v>
+      </c>
+      <c r="AN4">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>54</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40">
+      <c r="A6" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>8</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>8</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>8</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37">
-      <c r="A3">
-        <v>113</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>8</v>
-      </c>
-      <c r="J3">
-        <v>8</v>
-      </c>
-      <c r="K3">
-        <v>8</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>8</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>8</v>
-      </c>
-      <c r="Q3">
-        <v>8</v>
-      </c>
-      <c r="R3">
-        <v>8</v>
-      </c>
-      <c r="S3">
+      <c r="B6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>8</v>
+      </c>
+      <c r="M6">
+        <v>8</v>
+      </c>
+      <c r="N6" t="s">
+        <v>47</v>
+      </c>
+      <c r="O6" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6">
+        <v>8</v>
+      </c>
+      <c r="Q6">
+        <v>8</v>
+      </c>
+      <c r="R6">
+        <v>8</v>
+      </c>
+      <c r="S6">
+        <v>8</v>
+      </c>
+      <c r="T6">
+        <v>8</v>
+      </c>
+      <c r="U6" t="s">
+        <v>47</v>
+      </c>
+      <c r="V6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W6">
+        <v>8</v>
+      </c>
+      <c r="X6">
+        <v>8</v>
+      </c>
+      <c r="Y6">
+        <v>8</v>
+      </c>
+      <c r="Z6">
+        <v>8</v>
+      </c>
+      <c r="AA6">
         <v>4</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>8</v>
-      </c>
-      <c r="AA3">
-        <v>8</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37">
-      <c r="A4">
-        <v>113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>8</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>8</v>
-      </c>
-      <c r="AH4">
-        <v>8</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>0</v>
-      </c>
-      <c r="AK4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37">
-      <c r="A5">
-        <v>115</v>
-      </c>
-      <c r="B5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>8</v>
-      </c>
-      <c r="J5">
-        <v>8</v>
-      </c>
-      <c r="K5">
-        <v>8</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>8</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>8</v>
-      </c>
-      <c r="Q5">
-        <v>8</v>
-      </c>
-      <c r="R5">
-        <v>8</v>
-      </c>
-      <c r="S5">
-        <v>4</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>8</v>
-      </c>
-      <c r="AA5">
-        <v>8</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AH5">
-        <v>0</v>
-      </c>
-      <c r="AI5">
-        <v>0</v>
-      </c>
-      <c r="AJ5">
-        <v>0</v>
-      </c>
-      <c r="AK5">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37">
-      <c r="A6">
-        <v>115</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
+      <c r="AB6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>47</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE6">
         <v>8</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG6">
         <v>8</v>
@@ -2021,136 +2713,28 @@
       <c r="AH6">
         <v>8</v>
       </c>
-      <c r="AI6">
-        <v>0</v>
-      </c>
-      <c r="AJ6">
-        <v>0</v>
+      <c r="AI6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>47</v>
       </c>
       <c r="AK6">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7">
-        <v>8</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>8</v>
-      </c>
-      <c r="N7" t="s">
-        <v>49</v>
-      </c>
-      <c r="O7" t="s">
-        <v>49</v>
-      </c>
-      <c r="P7">
-        <v>8</v>
-      </c>
-      <c r="Q7">
-        <v>8</v>
-      </c>
-      <c r="R7">
-        <v>8</v>
-      </c>
-      <c r="S7">
-        <v>4</v>
-      </c>
-      <c r="T7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U7" t="s">
-        <v>49</v>
-      </c>
-      <c r="V7" t="s">
-        <v>49</v>
-      </c>
-      <c r="W7" t="s">
-        <v>49</v>
-      </c>
-      <c r="X7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z7">
-        <v>8</v>
-      </c>
-      <c r="AA7">
-        <v>8</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD7">
-        <v>8</v>
-      </c>
-      <c r="AE7">
-        <v>8</v>
-      </c>
-      <c r="AF7">
-        <v>8</v>
-      </c>
-      <c r="AG7">
-        <v>8</v>
-      </c>
-      <c r="AH7">
-        <v>8</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AK7">
-        <v>124</v>
+        <v>8</v>
+      </c>
+      <c r="AL6">
+        <v>8</v>
+      </c>
+      <c r="AM6">
+        <v>8</v>
+      </c>
+      <c r="AN6">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="test@gmail.com"/>
-    <hyperlink ref="C3" r:id="rId1" display="test@gmail.com"/>
-    <hyperlink ref="C4" r:id="rId1" display="test@gmail.com"/>
-    <hyperlink ref="C5" r:id="rId1" display="test`@gmail.com"/>
-    <hyperlink ref="C6" r:id="rId1" display="test`@gmail.com"/>
+    <hyperlink ref="C5" r:id="rId1" display="yash.upadhyaya@inferenz.ai"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
